--- a/Sample_Project/設計書/B1_顧客管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(Webサービス)_B10101_顧客検索.xlsx
+++ b/Sample_Project/設計書/B1_顧客管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(Webサービス)_B10101_顧客検索.xlsx
@@ -12543,8 +12543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -12585,8 +12585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -12621,8 +12621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -12659,8 +12659,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -12693,8 +12693,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -12727,8 +12727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -12761,8 +12761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -12795,8 +12795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -12833,8 +12833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -12867,8 +12867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -12901,8 +12901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -12937,8 +12937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -12971,8 +12971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -13005,8 +13005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -13039,8 +13039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -13077,8 +13077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -13111,8 +13111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -13149,8 +13149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -13183,8 +13183,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -13219,8 +13219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -13253,8 +13253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -13287,8 +13287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -13321,8 +13321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -13357,8 +13357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -13391,8 +13391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -13427,8 +13427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -13467,8 +13467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -13501,8 +13501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -13535,8 +13535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -13569,8 +13569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -13609,8 +13609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -13657,8 +13657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-3-1</v>
       </c>
@@ -13693,8 +13693,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-4-1</v>
       </c>
@@ -13741,8 +13741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -13783,8 +13783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -13817,8 +13817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -13851,8 +13851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -13887,8 +13887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -13921,8 +13921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -13955,8 +13955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -13991,8 +13991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -14025,8 +14025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -14061,8 +14061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -14095,8 +14095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -14129,8 +14129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -14163,8 +14163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -14197,8 +14197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -14231,8 +14231,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -14267,8 +14267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -14303,8 +14303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -14339,8 +14339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -14377,8 +14377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -14411,8 +14411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -14445,8 +14445,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -14479,8 +14479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -14513,8 +14513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -14549,8 +14549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -14583,8 +14583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -14617,8 +14617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -14651,8 +14651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -14685,8 +14685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -14719,8 +14719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -14753,8 +14753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -14787,8 +14787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -14823,8 +14823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -14859,8 +14859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -14893,8 +14893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -14927,8 +14927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -14961,8 +14961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -14995,8 +14995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -15035,8 +15035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -15069,8 +15069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -15105,8 +15105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -15141,8 +15141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -15175,8 +15175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -15211,8 +15211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -15247,8 +15247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -15287,8 +15287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -15323,8 +15323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -15359,8 +15359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -15399,8 +15399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -15433,8 +15433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -15469,8 +15469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -15505,8 +15505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -15539,8 +15539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -15575,8 +15575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -15615,8 +15615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -15649,8 +15649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -15683,8 +15683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -15717,8 +15717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -15751,8 +15751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -15787,8 +15787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -15821,8 +15821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -15855,8 +15855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -15889,8 +15889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -15923,8 +15923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -15959,8 +15959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -16001,8 +16001,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -16041,8 +16041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -16075,8 +16075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -16115,8 +16115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -16155,8 +16155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -16189,8 +16189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -16231,8 +16231,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -16267,8 +16267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -16301,8 +16301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -16335,8 +16335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -16371,8 +16371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -16405,8 +16405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -16439,8 +16439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -16473,8 +16473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -16507,8 +16507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -16543,8 +16543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -16577,8 +16577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -16611,8 +16611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -16645,8 +16645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -16679,8 +16679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -16715,8 +16715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -16753,8 +16753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -16793,8 +16793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -16829,8 +16829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -16863,8 +16863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -16897,8 +16897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -16939,8 +16939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -16975,8 +16975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -17009,8 +17009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -17043,8 +17043,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -17079,8 +17079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -17113,8 +17113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -17151,8 +17151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -17191,8 +17191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -17227,8 +17227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -17263,8 +17263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -17299,8 +17299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -17335,8 +17335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -17371,8 +17371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -17405,8 +17405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -17439,8 +17439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -17473,8 +17473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -17507,8 +17507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -17541,8 +17541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -17579,8 +17579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -17613,8 +17613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -17649,8 +17649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -17683,8 +17683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -17717,8 +17717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -17751,8 +17751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -17785,8 +17785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -17819,8 +17819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -17853,8 +17853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -17887,8 +17887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -17921,8 +17921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -17955,8 +17955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -17989,8 +17989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -18025,8 +18025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -18059,8 +18059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -18093,8 +18093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -18127,8 +18127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -18161,8 +18161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -18195,8 +18195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -18229,8 +18229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -18265,8 +18265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -18299,8 +18299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -18333,8 +18333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -18367,8 +18367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -18401,8 +18401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -18435,8 +18435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -18469,8 +18469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -18503,8 +18503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -18537,8 +18537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -18573,8 +18573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -18609,8 +18609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -18651,8 +18651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -18689,8 +18689,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -18727,8 +18727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -18769,8 +18769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -18805,8 +18805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -18839,8 +18839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -18875,8 +18875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -18909,8 +18909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -18947,8 +18947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -18987,8 +18987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -19021,8 +19021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -19055,8 +19055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -19089,8 +19089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -19123,8 +19123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -19157,8 +19157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -19191,8 +19191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -19227,8 +19227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -19265,8 +19265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -19299,8 +19299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -19333,8 +19333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -19367,8 +19367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -19401,8 +19401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -19435,8 +19435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -19469,8 +19469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -19503,8 +19503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -19537,8 +19537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -19571,8 +19571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -19605,8 +19605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -19639,8 +19639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -19673,8 +19673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -19711,8 +19711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -19745,8 +19745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -19779,8 +19779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -19813,8 +19813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -19847,8 +19847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -19881,8 +19881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -19915,8 +19915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -19949,8 +19949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -19983,8 +19983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -20017,8 +20017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -20051,8 +20051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -20085,8 +20085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -20119,8 +20119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -20153,8 +20153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -20187,8 +20187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -20223,8 +20223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -20257,8 +20257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -20291,8 +20291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -20327,8 +20327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -20363,8 +20363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -20405,8 +20405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -20441,8 +20441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -20475,8 +20475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -20509,8 +20509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -20543,8 +20543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -20577,8 +20577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -20613,8 +20613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -20647,8 +20647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -20681,8 +20681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -20715,8 +20715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -20749,8 +20749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -20785,8 +20785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -20825,8 +20825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -20867,8 +20867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -20901,8 +20901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -20939,8 +20939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -20973,8 +20973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -21013,8 +21013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -21049,8 +21049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -21085,8 +21085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -21121,8 +21121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -21159,8 +21159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -21193,8 +21193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -21229,8 +21229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -21263,8 +21263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -21297,8 +21297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -21331,8 +21331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -21365,8 +21365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -21399,8 +21399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -21433,8 +21433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -21467,8 +21467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -21501,8 +21501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -21535,8 +21535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -21569,8 +21569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -21605,8 +21605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -21639,8 +21639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -21673,8 +21673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -21707,8 +21707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -21741,8 +21741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -21775,8 +21775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -21811,8 +21811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -21845,8 +21845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -21879,8 +21879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -21913,8 +21913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -21947,8 +21947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -21981,8 +21981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -22015,8 +22015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -22049,8 +22049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -22085,8 +22085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -22127,8 +22127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -22161,8 +22161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -22195,8 +22195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -22229,8 +22229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -22269,8 +22269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -22305,8 +22305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -22341,8 +22341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -22377,8 +22377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -22415,8 +22415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -22449,8 +22449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -22483,8 +22483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -22517,8 +22517,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -22551,8 +22551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -22585,8 +22585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -22619,8 +22619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -22653,8 +22653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -22845,8 +22845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -22887,8 +22887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -22923,8 +22923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -22961,8 +22961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -22995,8 +22995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -23029,8 +23029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -23063,8 +23063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -23097,8 +23097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -23135,8 +23135,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -23169,8 +23169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -23203,8 +23203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -23239,8 +23239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -23273,8 +23273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -23307,8 +23307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -23341,8 +23341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -23379,8 +23379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -23413,8 +23413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -23451,8 +23451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -23485,8 +23485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -23521,8 +23521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -23555,8 +23555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -23589,8 +23589,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -23623,8 +23623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -23659,8 +23659,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -23693,8 +23693,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -23729,8 +23729,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -23769,8 +23769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -23803,8 +23803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -23837,8 +23837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -23871,8 +23871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -23909,8 +23909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -23943,8 +23943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -23985,8 +23985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -24019,8 +24019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -24053,8 +24053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -24089,8 +24089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -24123,8 +24123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -24157,8 +24157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -24193,8 +24193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -24227,8 +24227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -24263,8 +24263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -24297,8 +24297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -24331,8 +24331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -24365,8 +24365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -24399,8 +24399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -24433,8 +24433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -24469,8 +24469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -24505,8 +24505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -24541,8 +24541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -24579,8 +24579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -24613,8 +24613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -24647,8 +24647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -24681,8 +24681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -24715,8 +24715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -24751,8 +24751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -24785,8 +24785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -24819,8 +24819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -24853,8 +24853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -24887,8 +24887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -24921,8 +24921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -24955,8 +24955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -24989,8 +24989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -25025,8 +25025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -25061,8 +25061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -25095,8 +25095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -25129,8 +25129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -25163,8 +25163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -25197,8 +25197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -25237,8 +25237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -25271,8 +25271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -25307,8 +25307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -25343,8 +25343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -25377,8 +25377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -25413,8 +25413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -25449,8 +25449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -25489,8 +25489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -25525,8 +25525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -25561,8 +25561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -25601,8 +25601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -25635,8 +25635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -25671,8 +25671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -25707,8 +25707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -25741,8 +25741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -25777,8 +25777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -25817,8 +25817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -25851,8 +25851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -25885,8 +25885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -25919,8 +25919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -25953,8 +25953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -25989,8 +25989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -26023,8 +26023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -26057,8 +26057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -26091,8 +26091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -26125,8 +26125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -26161,8 +26161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -26203,8 +26203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -26243,8 +26243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -26277,8 +26277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -26317,8 +26317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -26357,8 +26357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -26391,8 +26391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -26433,8 +26433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -26469,8 +26469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -26503,8 +26503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -26537,8 +26537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -26573,8 +26573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -26607,8 +26607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -26641,8 +26641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -26675,8 +26675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -26709,8 +26709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -26745,8 +26745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -26779,8 +26779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -26813,8 +26813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -26847,8 +26847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -26881,8 +26881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -26917,8 +26917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -26955,8 +26955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -26995,8 +26995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -27031,8 +27031,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -27065,8 +27065,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -27099,8 +27099,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -27141,8 +27141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -27177,8 +27177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -27211,8 +27211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -27245,8 +27245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -27281,8 +27281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -27315,8 +27315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -27353,8 +27353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -27393,8 +27393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -27429,8 +27429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -27465,8 +27465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -27501,8 +27501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -27537,8 +27537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -27573,8 +27573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -27607,8 +27607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -27641,8 +27641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -27675,8 +27675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -27709,8 +27709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -27743,8 +27743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -27781,8 +27781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -27815,8 +27815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -27851,8 +27851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -27885,8 +27885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -27919,8 +27919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -27953,8 +27953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -27987,8 +27987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -28021,8 +28021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -28055,8 +28055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -28089,8 +28089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -28123,8 +28123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -28157,8 +28157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -28191,8 +28191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -28227,8 +28227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -28261,8 +28261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -28295,8 +28295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -28329,8 +28329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -28363,8 +28363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -28397,8 +28397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -28431,8 +28431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -28467,8 +28467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -28501,8 +28501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -28535,8 +28535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -28569,8 +28569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -28603,8 +28603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -28637,8 +28637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -28671,8 +28671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -28705,8 +28705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -28739,8 +28739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -28775,8 +28775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -28811,8 +28811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -28853,8 +28853,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -28891,8 +28891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -28929,8 +28929,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -28971,8 +28971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -29007,8 +29007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -29041,8 +29041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -29077,8 +29077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -29111,8 +29111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -29149,8 +29149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -29189,8 +29189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -29223,8 +29223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -29257,8 +29257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -29291,8 +29291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -29325,8 +29325,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -29359,8 +29359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -29393,8 +29393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -29429,8 +29429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -29467,8 +29467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -29501,8 +29501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -29535,8 +29535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -29569,8 +29569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -29603,8 +29603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -29637,8 +29637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -29671,8 +29671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -29705,8 +29705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -29739,8 +29739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -29773,8 +29773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -29807,8 +29807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -29841,8 +29841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -29875,8 +29875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -29913,8 +29913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -29947,8 +29947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -29981,8 +29981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -30015,8 +30015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -30049,8 +30049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -30083,8 +30083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -30117,8 +30117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -30151,8 +30151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -30185,8 +30185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -30219,8 +30219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -30253,8 +30253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -30287,8 +30287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -30321,8 +30321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -30355,8 +30355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -30389,8 +30389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -30425,8 +30425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -30459,8 +30459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -30493,8 +30493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -30529,8 +30529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -30565,8 +30565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -30607,8 +30607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -30643,8 +30643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -30677,8 +30677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -30711,8 +30711,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -30745,8 +30745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -30779,8 +30779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -30815,8 +30815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -30849,8 +30849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -30883,8 +30883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -30917,8 +30917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -30951,8 +30951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -30987,8 +30987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -31027,8 +31027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -31069,8 +31069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -31103,8 +31103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -31141,8 +31141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -31175,8 +31175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -31215,8 +31215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -31251,8 +31251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -31287,8 +31287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -31323,8 +31323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -31361,8 +31361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -31395,8 +31395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -31431,8 +31431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -31465,8 +31465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -31499,8 +31499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -31533,8 +31533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -31567,8 +31567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -31601,8 +31601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -31635,8 +31635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -31669,8 +31669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -31703,8 +31703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -31737,8 +31737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -31771,8 +31771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -31807,8 +31807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -31841,8 +31841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -31875,8 +31875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -31909,8 +31909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -31943,8 +31943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -31977,8 +31977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -32013,8 +32013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -32047,8 +32047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -32081,8 +32081,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -32115,8 +32115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -32149,8 +32149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -32183,8 +32183,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -32217,8 +32217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -32251,8 +32251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -32287,8 +32287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -32329,8 +32329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -32363,8 +32363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -32397,8 +32397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -32431,8 +32431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -32471,8 +32471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -32507,8 +32507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -32543,8 +32543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -32579,8 +32579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -32617,8 +32617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -32651,8 +32651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -32685,8 +32685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -32719,8 +32719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -32753,8 +32753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -32787,8 +32787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -32821,8 +32821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -32855,8 +32855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -33063,8 +33063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -33106,8 +33106,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -33143,8 +33143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -33182,8 +33182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -33217,8 +33217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -33252,8 +33252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -33287,8 +33287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -33322,8 +33322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -33361,8 +33361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -33396,8 +33396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -33431,8 +33431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -33468,8 +33468,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -33503,8 +33503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -33538,8 +33538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -33573,8 +33573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -33612,8 +33612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -33647,8 +33647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -33686,8 +33686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -33721,8 +33721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -33758,8 +33758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -33793,8 +33793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -33828,8 +33828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -33863,8 +33863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -33900,8 +33900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -33935,8 +33935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -33972,8 +33972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -34013,8 +34013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -34048,8 +34048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -34083,8 +34083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -34118,8 +34118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -34157,8 +34157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -34192,8 +34192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -34247,8 +34247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -34296,8 +34296,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -34335,8 +34335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -34370,8 +34370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -34427,8 +34427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-2</v>
       </c>
@@ -34474,8 +34474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -34523,8 +34523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-2</v>
       </c>
@@ -34572,8 +34572,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-1</v>
       </c>
@@ -34621,8 +34621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-2</v>
       </c>
@@ -34668,8 +34668,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-3</v>
       </c>
@@ -34715,8 +34715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-4</v>
       </c>
@@ -34764,8 +34764,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -34815,8 +34815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -34864,8 +34864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -34913,8 +34913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -34964,8 +34964,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-2-1</v>
       </c>
@@ -35015,8 +35015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -35066,8 +35066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-2-1</v>
       </c>
@@ -35115,8 +35115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-3-1</v>
       </c>
@@ -35150,8 +35150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-4-1</v>
       </c>
@@ -35185,8 +35185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-5-1</v>
       </c>
@@ -35220,8 +35220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-6-1</v>
       </c>
@@ -35255,8 +35255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -35292,8 +35292,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -35329,8 +35329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -35382,8 +35382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -35421,8 +35421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-2-1</v>
       </c>
@@ -35456,8 +35456,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-3-1</v>
       </c>
@@ -35491,8 +35491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-4-1</v>
       </c>
@@ -35526,8 +35526,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-5-1</v>
       </c>
@@ -35561,8 +35561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -35598,8 +35598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -35633,8 +35633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -35668,8 +35668,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -35703,8 +35703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -35738,8 +35738,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-6-1</v>
       </c>
@@ -35773,8 +35773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-7-1</v>
       </c>
@@ -35808,8 +35808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-8-1</v>
       </c>
@@ -35843,8 +35843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -35880,8 +35880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -35917,8 +35917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-2-1</v>
       </c>
@@ -35952,8 +35952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-3-1</v>
       </c>
@@ -35987,8 +35987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-4-1</v>
       </c>
@@ -36022,8 +36022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-5-1</v>
       </c>
@@ -36057,8 +36057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -36111,8 +36111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-2</v>
       </c>
@@ -36157,8 +36157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-3</v>
       </c>
@@ -36203,8 +36203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-4</v>
       </c>
@@ -36249,8 +36249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -36300,8 +36300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -36351,8 +36351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-2</v>
       </c>
@@ -36398,8 +36398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-3</v>
       </c>
@@ -36447,8 +36447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -36484,8 +36484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-2-1</v>
       </c>
@@ -36519,8 +36519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -36570,8 +36570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -36607,8 +36607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -36648,8 +36648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -36685,8 +36685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -36722,8 +36722,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -36763,8 +36763,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -36798,8 +36798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -36835,8 +36835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -36872,8 +36872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -36907,8 +36907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -36944,8 +36944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -36985,8 +36985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-2-1</v>
       </c>
@@ -37020,8 +37020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-3-1</v>
       </c>
@@ -37055,8 +37055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-4-1</v>
       </c>
@@ -37090,8 +37090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-5-1</v>
       </c>
@@ -37125,8 +37125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -37162,8 +37162,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-2-1</v>
       </c>
@@ -37197,8 +37197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-3-1</v>
       </c>
@@ -37232,8 +37232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-4-1</v>
       </c>
@@ -37267,8 +37267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-5-1</v>
       </c>
@@ -37302,8 +37302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -37339,8 +37339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -37382,8 +37382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -37423,8 +37423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -37458,8 +37458,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -37499,8 +37499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -37540,8 +37540,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -37575,8 +37575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -37618,8 +37618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -37655,8 +37655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -37690,8 +37690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -37725,8 +37725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -37762,8 +37762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-2-1</v>
       </c>
@@ -37797,8 +37797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-3-1</v>
       </c>
@@ -37832,8 +37832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-4-1</v>
       </c>
@@ -37867,8 +37867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-5-1</v>
       </c>
@@ -37902,8 +37902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -37939,8 +37939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-2-1</v>
       </c>
@@ -37974,8 +37974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-3-1</v>
       </c>
@@ -38009,8 +38009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-4-1</v>
       </c>
@@ -38044,8 +38044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-5-1</v>
       </c>
@@ -38079,8 +38079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -38116,8 +38116,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -38155,8 +38155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -38196,8 +38196,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -38233,8 +38233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -38268,8 +38268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-3-1</v>
       </c>
@@ -38303,8 +38303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -38346,8 +38346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-2-1</v>
       </c>
@@ -38383,8 +38383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-3-1</v>
       </c>
@@ -38418,8 +38418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-4-1</v>
       </c>
@@ -38453,8 +38453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -38490,8 +38490,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-2-1</v>
       </c>
@@ -38525,8 +38525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -38564,8 +38564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -38605,8 +38605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -38642,8 +38642,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -38679,8 +38679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -38716,8 +38716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -38753,8 +38753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -38790,8 +38790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -38825,8 +38825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -38860,8 +38860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -38895,8 +38895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -38930,8 +38930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -38965,8 +38965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -39004,8 +39004,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -39039,8 +39039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -39076,8 +39076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -39111,8 +39111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -39146,8 +39146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -39181,8 +39181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -39216,8 +39216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -39251,8 +39251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -39286,8 +39286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -39321,8 +39321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -39356,8 +39356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-10-1</v>
       </c>
@@ -39391,8 +39391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-11-1</v>
       </c>
@@ -39426,8 +39426,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -39463,8 +39463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-2-1</v>
       </c>
@@ -39498,8 +39498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-3-1</v>
       </c>
@@ -39533,8 +39533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-4-1</v>
       </c>
@@ -39568,8 +39568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-5-1</v>
       </c>
@@ -39603,8 +39603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-6-1</v>
       </c>
@@ -39638,8 +39638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-7-1</v>
       </c>
@@ -39673,8 +39673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -39710,8 +39710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-2-1</v>
       </c>
@@ -39745,8 +39745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-3-1</v>
       </c>
@@ -39780,8 +39780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-4-1</v>
       </c>
@@ -39815,8 +39815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-5-1</v>
       </c>
@@ -39850,8 +39850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-6-1</v>
       </c>
@@ -39885,8 +39885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-7-1</v>
       </c>
@@ -39920,8 +39920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-8-1</v>
       </c>
@@ -39955,8 +39955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-9-1</v>
       </c>
@@ -39990,8 +39990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -40027,8 +40027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -40064,8 +40064,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -40107,8 +40107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -40146,8 +40146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -40185,8 +40185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -40228,8 +40228,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -40265,8 +40265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-2-1</v>
       </c>
@@ -40300,8 +40300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -40337,8 +40337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -40372,8 +40372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -40411,8 +40411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -40452,8 +40452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -40487,8 +40487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -40522,8 +40522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -40557,8 +40557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -40592,8 +40592,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -40627,8 +40627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -40662,8 +40662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -40699,8 +40699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -40738,8 +40738,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -40773,8 +40773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -40808,8 +40808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-4-1</v>
       </c>
@@ -40843,8 +40843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-5-1</v>
       </c>
@@ -40878,8 +40878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-6-1</v>
       </c>
@@ -40913,8 +40913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-7-1</v>
       </c>
@@ -40948,8 +40948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-8-1</v>
       </c>
@@ -40983,8 +40983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-9-1</v>
       </c>
@@ -41018,8 +41018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-10-1</v>
       </c>
@@ -41053,8 +41053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-11-1</v>
       </c>
@@ -41088,8 +41088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-12-1</v>
       </c>
@@ -41123,8 +41123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-13-1</v>
       </c>
@@ -41158,8 +41158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -41197,8 +41197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-2-1</v>
       </c>
@@ -41232,8 +41232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-3-1</v>
       </c>
@@ -41267,8 +41267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-4-1</v>
       </c>
@@ -41302,8 +41302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-5-1</v>
       </c>
@@ -41337,8 +41337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-6-1</v>
       </c>
@@ -41372,8 +41372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-7-1</v>
       </c>
@@ -41407,8 +41407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-8-1</v>
       </c>
@@ -41442,8 +41442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-9-1</v>
       </c>
@@ -41477,8 +41477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-10-1</v>
       </c>
@@ -41512,8 +41512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-11-1</v>
       </c>
@@ -41547,8 +41547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-12-1</v>
       </c>
@@ -41582,8 +41582,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-13-1</v>
       </c>
@@ -41617,8 +41617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-14-1</v>
       </c>
@@ -41652,8 +41652,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-15-1</v>
       </c>
@@ -41687,8 +41687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -41724,8 +41724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-2-1</v>
       </c>
@@ -41759,8 +41759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-3-1</v>
       </c>
@@ -41794,8 +41794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -41831,8 +41831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -41868,8 +41868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -41911,8 +41911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -41948,8 +41948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-2-1</v>
       </c>
@@ -41983,8 +41983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-3-1</v>
       </c>
@@ -42018,8 +42018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-4-1</v>
       </c>
@@ -42053,8 +42053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-5-1</v>
       </c>
@@ -42088,8 +42088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -42125,8 +42125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-2-1</v>
       </c>
@@ -42160,8 +42160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-3-1</v>
       </c>
@@ -42195,8 +42195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-4-1</v>
       </c>
@@ -42230,8 +42230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-5-1</v>
       </c>
@@ -42265,8 +42265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -42302,8 +42302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -42343,8 +42343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -42386,8 +42386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-2-1</v>
       </c>
@@ -42421,8 +42421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -42460,8 +42460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-2-1</v>
       </c>
@@ -42495,8 +42495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -42536,8 +42536,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -42573,8 +42573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -42610,8 +42610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -42647,8 +42647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -42686,8 +42686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -42721,8 +42721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -42758,8 +42758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -42793,8 +42793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -42828,8 +42828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -42863,8 +42863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -42898,8 +42898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -42933,8 +42933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -42968,8 +42968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -43003,8 +43003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-9-1</v>
       </c>
@@ -43038,8 +43038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-10-1</v>
       </c>
@@ -43073,8 +43073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-11-1</v>
       </c>
@@ -43108,8 +43108,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -43145,8 +43145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-2-1</v>
       </c>
@@ -43180,8 +43180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-3-1</v>
       </c>
@@ -43215,8 +43215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-4-1</v>
       </c>
@@ -43250,8 +43250,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-5-1</v>
       </c>
@@ -43285,8 +43285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-6-1</v>
       </c>
@@ -43320,8 +43320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -43357,8 +43357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -43392,8 +43392,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -43427,8 +43427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -43462,8 +43462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-5-1</v>
       </c>
@@ -43497,8 +43497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-6-1</v>
       </c>
@@ -43532,8 +43532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-7-1</v>
       </c>
@@ -43567,8 +43567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-8-1</v>
       </c>
@@ -43602,8 +43602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -43639,8 +43639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -43682,8 +43682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-2-1</v>
       </c>
@@ -43717,8 +43717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-3-1</v>
       </c>
@@ -43752,8 +43752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-4-1</v>
       </c>
@@ -43787,8 +43787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -43828,8 +43828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -43865,8 +43865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -43902,8 +43902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -43939,8 +43939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -43978,8 +43978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -44013,8 +44013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-3-1</v>
       </c>
@@ -44048,8 +44048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-4-1</v>
       </c>
@@ -44083,8 +44083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-5-1</v>
       </c>
@@ -44118,8 +44118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-6-1</v>
       </c>
@@ -44153,8 +44153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-7-1</v>
       </c>
@@ -44188,8 +44188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-8-1</v>
       </c>
@@ -44223,8 +44223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-9-1</v>
       </c>
@@ -44258,8 +44258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -44315,8 +44315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -44368,8 +44368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-2</v>
       </c>
@@ -44415,8 +44415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-3</v>
       </c>
@@ -44464,8 +44464,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -44517,8 +44517,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -44566,8 +44566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -44601,8 +44601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -44640,8 +44640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -44677,8 +44677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -44730,8 +44730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-2</v>
       </c>
@@ -44779,8 +44779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F321),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F321)&gt;0)*ROW($F$11:F321),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J321),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-2-1</v>
       </c>
@@ -44828,8 +44828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F322),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F322)&gt;0)*ROW($F$11:F322),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J322),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-3-1</v>
       </c>
@@ -44863,8 +44863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F323),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F323)&gt;0)*ROW($F$11:F323),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J323),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-4-1</v>
       </c>
@@ -44898,8 +44898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F324),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F324)&gt;0)*ROW($F$11:F324),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J324),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-5-1</v>
       </c>
@@ -44933,8 +44933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F325),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F325)&gt;0)*ROW($F$11:F325),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J325),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-6-1</v>
       </c>
@@ -44968,8 +44968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F326),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F326)&gt;0)*ROW($F$11:F326),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J326),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-7-1</v>
       </c>
@@ -45003,8 +45003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F327),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F327)&gt;0)*ROW($F$11:F327),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J327),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-8-1</v>
       </c>
